--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.51832932476167</v>
+        <v>10.97172851527377</v>
       </c>
       <c r="D2" t="n">
-        <v>20.48475211235853</v>
+        <v>3.328772218258261</v>
       </c>
       <c r="E2" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F2" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.5898051802095</v>
+        <v>9.520843341784044</v>
       </c>
       <c r="D3" t="n">
-        <v>26.74036637515558</v>
+        <v>4.345309535962782</v>
       </c>
       <c r="E3" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F3" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.0132479707078</v>
+        <v>6.339652795240018</v>
       </c>
       <c r="D4" t="n">
-        <v>38.99665060213749</v>
+        <v>6.336955722847342</v>
       </c>
       <c r="E4" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F4" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.70538948591005</v>
+        <v>6.939625791460383</v>
       </c>
       <c r="D5" t="n">
-        <v>42.63333999160346</v>
+        <v>6.927917748635563</v>
       </c>
       <c r="E5" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F5" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.11698118395746</v>
+        <v>8.469009442393087</v>
       </c>
       <c r="D6" t="n">
-        <v>52.07899131302433</v>
+        <v>8.462836088366455</v>
       </c>
       <c r="E6" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F6" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.64117224121433</v>
+        <v>9.041690489197329</v>
       </c>
       <c r="D7" t="n">
-        <v>55.53469923720975</v>
+        <v>9.024388626046585</v>
       </c>
       <c r="E7" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F7" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>69.63057973835508</v>
+        <v>11.3149692074827</v>
       </c>
       <c r="D8" t="n">
-        <v>69.52248841375695</v>
+        <v>11.2974043672355</v>
       </c>
       <c r="E8" t="n">
-        <v>10.68442850022023</v>
+        <v>1.736219631285788</v>
       </c>
       <c r="F8" t="n">
-        <v>15.70670232344876</v>
+        <v>2.552339127560423</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
